--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.93790186311217</v>
+        <v>4.052409052755728</v>
       </c>
       <c r="D2" t="n">
-        <v>25.1963610141473</v>
+        <v>4.094408664798936</v>
       </c>
       <c r="E2" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F2" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.84309995682833</v>
+        <v>3.224503742984604</v>
       </c>
       <c r="D3" t="n">
-        <v>19.91389411858762</v>
+        <v>3.236007794270488</v>
       </c>
       <c r="E3" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F3" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.09392055773305</v>
+        <v>4.890262090631621</v>
       </c>
       <c r="D4" t="n">
-        <v>29.9792867910137</v>
+        <v>4.871634103539727</v>
       </c>
       <c r="E4" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F4" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.55835944494623</v>
+        <v>6.103233409803762</v>
       </c>
       <c r="D5" t="n">
-        <v>37.35655500266122</v>
+        <v>6.070440187932449</v>
       </c>
       <c r="E5" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F5" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.25293839824324</v>
+        <v>2.316102489714527</v>
       </c>
       <c r="D6" t="n">
-        <v>14.46757236888502</v>
+        <v>2.350980509943815</v>
       </c>
       <c r="E6" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F6" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.13301543980613</v>
+        <v>4.734115008968496</v>
       </c>
       <c r="D7" t="n">
-        <v>29.19731406165317</v>
+        <v>4.74456353501864</v>
       </c>
       <c r="E7" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F7" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.88040932535383</v>
+        <v>5.830566515369997</v>
       </c>
       <c r="D8" t="n">
-        <v>36.03550024825287</v>
+        <v>5.855768790341091</v>
       </c>
       <c r="E8" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F8" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.38877241408593</v>
+        <v>7.538175517288964</v>
       </c>
       <c r="D9" t="n">
-        <v>27.04368893311544</v>
+        <v>4.394599451631259</v>
       </c>
       <c r="E9" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F9" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.44521463759731</v>
+        <v>5.272347378609563</v>
       </c>
       <c r="D10" t="n">
-        <v>10.75613520017504</v>
+        <v>1.747871970028444</v>
       </c>
       <c r="E10" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F10" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.97614960132502</v>
+        <v>5.846124310215316</v>
       </c>
       <c r="D11" t="n">
-        <v>26.65699884202721</v>
+        <v>4.331762311829421</v>
       </c>
       <c r="E11" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F11" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>43.87264066352657</v>
+        <v>7.129304107823067</v>
       </c>
       <c r="D12" t="n">
-        <v>27.65310912798856</v>
+        <v>4.49363023329814</v>
       </c>
       <c r="E12" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F12" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>13.71898425731456</v>
+        <v>2.229334941813616</v>
       </c>
       <c r="D13" t="n">
-        <v>13.76876585424968</v>
+        <v>2.237424451315573</v>
       </c>
       <c r="E13" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F13" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>15.84769928584722</v>
+        <v>2.575251133950173</v>
       </c>
       <c r="D14" t="n">
-        <v>16.04032701988664</v>
+        <v>2.606553140731579</v>
       </c>
       <c r="E14" t="n">
-        <v>10.48643681559012</v>
+        <v>1.704045982533395</v>
       </c>
       <c r="F14" t="n">
-        <v>8.170230684731461</v>
+        <v>1.327662486268862</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
